--- a/import-files/Upper Placement Logs.xlsx
+++ b/import-files/Upper Placement Logs.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Downloads\New folder (2)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Downloads\New folder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C586F76D-03F6-484E-A306-BCCBB4534025}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26AE31AC-CAE4-4B63-88D8-827DCDE973C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-109" yWindow="-109" windowWidth="26301" windowHeight="14169" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="25974" yWindow="-109" windowWidth="26301" windowHeight="14169" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -691,43 +691,43 @@
         <v>20</v>
       </c>
       <c r="D2" s="8">
-        <v>142681</v>
+        <v>165338</v>
       </c>
       <c r="E2" s="8">
-        <v>6142</v>
+        <v>7089</v>
       </c>
       <c r="F2" s="9">
-        <v>69.691142950179099</v>
+        <v>69.96953025814642</v>
       </c>
       <c r="G2" s="8">
-        <v>507</v>
+        <v>593</v>
       </c>
       <c r="H2" s="8">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="I2" s="8">
         <v>0</v>
       </c>
       <c r="J2" s="8">
-        <v>304</v>
+        <v>352</v>
       </c>
       <c r="K2" s="8">
-        <v>203</v>
+        <v>235</v>
       </c>
       <c r="L2" s="8">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="M2" s="8">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="N2" s="10">
-        <v>0.66776315789473684</v>
+        <v>0.66761363636363635</v>
       </c>
       <c r="O2" s="11">
+        <v>15</v>
+      </c>
+      <c r="P2" s="11">
         <v>13</v>
-      </c>
-      <c r="P2" s="11">
-        <v>11</v>
       </c>
       <c r="Q2" s="11">
         <v>1</v>
@@ -736,7 +736,7 @@
         <v>1</v>
       </c>
       <c r="S2" s="11">
-        <v>34</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3" spans="1:21" s="5" customFormat="1" ht="21.1" x14ac:dyDescent="0.25">
@@ -750,52 +750,52 @@
         <v>20</v>
       </c>
       <c r="D3" s="17">
-        <v>141742</v>
+        <v>163414</v>
       </c>
       <c r="E3" s="17">
-        <v>6310</v>
+        <v>7267</v>
       </c>
       <c r="F3" s="18">
-        <v>67.389223454833598</v>
+        <v>67.461400853171881</v>
       </c>
       <c r="G3" s="17">
-        <v>452</v>
+        <v>517</v>
       </c>
       <c r="H3" s="17">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I3" s="17">
         <v>2</v>
       </c>
       <c r="J3" s="17">
-        <v>304</v>
+        <v>352</v>
       </c>
       <c r="K3" s="17">
-        <v>189</v>
+        <v>210</v>
       </c>
       <c r="L3" s="17">
-        <v>115</v>
+        <v>142</v>
       </c>
       <c r="M3" s="17">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="N3" s="19">
-        <v>0.62171052631578949</v>
+        <v>0.59659090909090906</v>
       </c>
       <c r="O3" s="17">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="P3" s="17">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Q3" s="17">
         <v>0</v>
       </c>
       <c r="R3" s="17">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S3" s="17">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:21" s="5" customFormat="1" ht="21.1" x14ac:dyDescent="0.25">
@@ -809,52 +809,52 @@
         <v>20</v>
       </c>
       <c r="D4" s="17">
-        <v>141254</v>
+        <v>162643</v>
       </c>
       <c r="E4" s="17">
-        <v>6533</v>
+        <v>7537</v>
       </c>
       <c r="F4" s="18">
-        <v>64.864840042859328</v>
+        <v>64.737826721507233</v>
       </c>
       <c r="G4" s="17">
-        <v>416</v>
+        <v>461</v>
       </c>
       <c r="H4" s="17">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="I4" s="17">
         <v>0</v>
       </c>
       <c r="J4" s="17">
-        <v>304</v>
+        <v>352</v>
       </c>
       <c r="K4" s="17">
-        <v>182</v>
+        <v>206</v>
       </c>
       <c r="L4" s="17">
-        <v>122</v>
+        <v>146</v>
       </c>
       <c r="M4" s="17">
         <v>60</v>
       </c>
       <c r="N4" s="19">
-        <v>0.59868421052631582</v>
+        <v>0.58522727272727271</v>
       </c>
       <c r="O4" s="17">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="P4" s="17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q4" s="17">
         <v>3</v>
       </c>
       <c r="R4" s="17">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S4" s="17">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:21" s="5" customFormat="1" ht="21.1" x14ac:dyDescent="0.25">
@@ -868,52 +868,52 @@
         <v>20</v>
       </c>
       <c r="D5" s="17">
-        <v>140585</v>
+        <v>163245</v>
       </c>
       <c r="E5" s="17">
-        <v>6525</v>
+        <v>7553</v>
       </c>
       <c r="F5" s="18">
-        <v>64.636781609195396</v>
+        <v>64.839798755461402</v>
       </c>
       <c r="G5" s="17">
-        <v>377</v>
+        <v>454</v>
       </c>
       <c r="H5" s="17">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="I5" s="17">
         <v>1</v>
       </c>
       <c r="J5" s="17">
-        <v>304</v>
+        <v>352</v>
       </c>
       <c r="K5" s="17">
-        <v>172</v>
+        <v>198</v>
       </c>
       <c r="L5" s="17">
-        <v>132</v>
+        <v>154</v>
       </c>
       <c r="M5" s="17">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="N5" s="19">
-        <v>0.56578947368421051</v>
+        <v>0.5625</v>
       </c>
       <c r="O5" s="17">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="P5" s="17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q5" s="17">
         <v>0</v>
       </c>
       <c r="R5" s="17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S5" s="17">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:21" s="5" customFormat="1" ht="21.1" x14ac:dyDescent="0.25">
@@ -927,52 +927,52 @@
         <v>20</v>
       </c>
       <c r="D6" s="17">
-        <v>138743</v>
+        <v>160287</v>
       </c>
       <c r="E6" s="17">
-        <v>6551</v>
+        <v>7610</v>
       </c>
       <c r="F6" s="18">
-        <v>63.536711952373679</v>
+        <v>63.188042049934296</v>
       </c>
       <c r="G6" s="17">
-        <v>418</v>
+        <v>488</v>
       </c>
       <c r="H6" s="17">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="I6" s="17">
         <v>0</v>
       </c>
       <c r="J6" s="17">
-        <v>304</v>
+        <v>352</v>
       </c>
       <c r="K6" s="17">
-        <v>155</v>
+        <v>180</v>
       </c>
       <c r="L6" s="17">
-        <v>149</v>
+        <v>172</v>
       </c>
       <c r="M6" s="17">
+        <v>8</v>
+      </c>
+      <c r="N6" s="19">
+        <v>0.51136363636363635</v>
+      </c>
+      <c r="O6" s="17">
+        <v>15</v>
+      </c>
+      <c r="P6" s="17">
         <v>6</v>
-      </c>
-      <c r="N6" s="19">
-        <v>0.50986842105263153</v>
-      </c>
-      <c r="O6" s="17">
-        <v>13</v>
-      </c>
-      <c r="P6" s="17">
-        <v>5</v>
       </c>
       <c r="Q6" s="17">
         <v>1</v>
       </c>
       <c r="R6" s="17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S6" s="17">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:21" s="5" customFormat="1" ht="21.1" x14ac:dyDescent="0.25">
@@ -980,58 +980,58 @@
         <v>6</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C7" s="16" t="s">
         <v>20</v>
       </c>
       <c r="D7" s="17">
-        <v>131104</v>
+        <v>155462</v>
       </c>
       <c r="E7" s="17">
-        <v>6899</v>
+        <v>7936</v>
       </c>
       <c r="F7" s="18">
-        <v>57.010001449485429</v>
+        <v>58.768397177419359</v>
       </c>
       <c r="G7" s="17">
-        <v>279</v>
+        <v>420</v>
       </c>
       <c r="H7" s="17">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I7" s="17">
         <v>0</v>
       </c>
       <c r="J7" s="17">
-        <v>304</v>
+        <v>352</v>
       </c>
       <c r="K7" s="17">
-        <v>113</v>
+        <v>153</v>
       </c>
       <c r="L7" s="17">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="M7" s="17">
-        <v>-78</v>
+        <v>-46</v>
       </c>
       <c r="N7" s="19">
-        <v>0.37171052631578949</v>
+        <v>0.43465909090909088</v>
       </c>
       <c r="O7" s="17">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="P7" s="17">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q7" s="17">
         <v>2</v>
       </c>
       <c r="R7" s="17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="S7" s="17">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:21" s="5" customFormat="1" ht="21.1" x14ac:dyDescent="0.25">
@@ -1039,58 +1039,58 @@
         <v>7</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C8" s="16" t="s">
         <v>20</v>
       </c>
       <c r="D8" s="17">
-        <v>133032</v>
+        <v>151963</v>
       </c>
       <c r="E8" s="17">
-        <v>6736</v>
+        <v>8070</v>
       </c>
       <c r="F8" s="18">
-        <v>59.248218527315913</v>
+        <v>56.491821561338298</v>
       </c>
       <c r="G8" s="17">
-        <v>364</v>
+        <v>318</v>
       </c>
       <c r="H8" s="17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I8" s="17">
         <v>0</v>
       </c>
       <c r="J8" s="17">
-        <v>304</v>
+        <v>352</v>
       </c>
       <c r="K8" s="17">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="L8" s="17">
-        <v>182</v>
+        <v>219</v>
       </c>
       <c r="M8" s="17">
-        <v>-60</v>
+        <v>-86</v>
       </c>
       <c r="N8" s="19">
-        <v>0.40131578947368424</v>
+        <v>0.37784090909090912</v>
       </c>
       <c r="O8" s="17">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="P8" s="17">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q8" s="17">
         <v>2</v>
       </c>
       <c r="R8" s="17">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="S8" s="17">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:21" s="5" customFormat="1" ht="21.1" x14ac:dyDescent="0.25">
@@ -1104,16 +1104,16 @@
         <v>20</v>
       </c>
       <c r="D9" s="17">
-        <v>127853</v>
+        <v>147282</v>
       </c>
       <c r="E9" s="17">
-        <v>7022</v>
+        <v>8147</v>
       </c>
       <c r="F9" s="18">
-        <v>54.622472230133866</v>
+        <v>54.234196636798821</v>
       </c>
       <c r="G9" s="17">
-        <v>296</v>
+        <v>332</v>
       </c>
       <c r="H9" s="17">
         <v>7</v>
@@ -1122,22 +1122,22 @@
         <v>0</v>
       </c>
       <c r="J9" s="17">
-        <v>304</v>
+        <v>352</v>
       </c>
       <c r="K9" s="17">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="L9" s="17">
-        <v>224</v>
+        <v>259</v>
       </c>
       <c r="M9" s="17">
-        <v>-144</v>
+        <v>-166</v>
       </c>
       <c r="N9" s="19">
-        <v>0.26315789473684209</v>
+        <v>0.26420454545454547</v>
       </c>
       <c r="O9" s="17">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="P9" s="17">
         <v>0</v>
@@ -1146,7 +1146,7 @@
         <v>1</v>
       </c>
       <c r="R9" s="17">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="S9" s="17">
         <v>1</v>
